--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 10/02. Trả bảo hành/TBH_.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 10/02. Trả bảo hành/TBH_.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 03\02. Trả bảo hành\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 10\02. Trả bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4131B20-101D-4C74-88D4-DE56F13A7D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D660F587-54EA-4DE3-91D2-C315F3CEC74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -85,13 +85,13 @@
     <t>Phí Sửa Chữa</t>
   </si>
   <si>
-    <t>TBP. Bảo Hành</t>
-  </si>
-  <si>
     <t>Người Lập</t>
   </si>
   <si>
     <t>Hà Nội, ngày   tháng   năm 202</t>
+  </si>
+  <si>
+    <t>Xác Nhận Bảo Hành</t>
   </si>
 </sst>
 </file>
@@ -474,6 +474,30 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="18"/>
     </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -505,30 +529,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -912,92 +912,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="45"/>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="46" t="s">
+      <c r="A1" s="53"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
     </row>
     <row r="2" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="47" t="s">
+      <c r="A2" s="53"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="49"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="57"/>
     </row>
     <row r="3" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="50" t="s">
+      <c r="A3" s="53"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="52"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="60"/>
     </row>
     <row r="4" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="45"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="53" t="s">
+      <c r="A4" s="53"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="55"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="56" t="s">
+      <c r="A5" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
     </row>
     <row r="6" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="59"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
       <c r="E6" s="25"/>
       <c r="F6" s="23"/>
       <c r="G6" s="23"/>
       <c r="H6" s="23"/>
-      <c r="I6" s="60" t="s">
-        <v>22</v>
+      <c r="I6" s="45" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
       <c r="E7" s="25"/>
       <c r="F7" s="24"/>
       <c r="G7" s="24"/>
@@ -1005,12 +1005,12 @@
       <c r="I7" s="24"/>
     </row>
     <row r="8" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
       <c r="E8" s="25"/>
       <c r="F8" s="23"/>
       <c r="G8" s="23"/>
@@ -1018,12 +1018,12 @@
       <c r="I8" s="23"/>
     </row>
     <row r="9" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="59" t="s">
+      <c r="A9" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="59"/>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
       <c r="E9" s="25"/>
       <c r="F9" s="23"/>
       <c r="G9" s="23"/>
@@ -1061,27 +1061,27 @@
       <c r="J10" s="7"/>
     </row>
     <row r="11" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="61"/>
-      <c r="B11" s="61"/>
-      <c r="C11" s="62"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="62"/>
-      <c r="F11" s="62"/>
-      <c r="G11" s="62"/>
-      <c r="H11" s="62"/>
-      <c r="I11" s="63"/>
+      <c r="A11" s="46"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="48"/>
       <c r="J11" s="7"/>
     </row>
     <row r="12" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="61"/>
-      <c r="B12" s="61"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="62"/>
-      <c r="E12" s="62"/>
-      <c r="F12" s="62"/>
-      <c r="G12" s="62"/>
-      <c r="H12" s="62"/>
-      <c r="I12" s="63"/>
+      <c r="A12" s="46"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="48"/>
       <c r="J12" s="7"/>
     </row>
     <row r="13" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1121,7 +1121,7 @@
     </row>
     <row r="16" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="38" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B16" s="15"/>
       <c r="C16" s="15"/>
@@ -1129,7 +1129,7 @@
       <c r="E16" s="15"/>
       <c r="F16" s="13"/>
       <c r="G16" s="42" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H16" s="35"/>
       <c r="I16" s="35"/>
@@ -1229,23 +1229,23 @@
       <c r="I24" s="19"/>
     </row>
     <row r="26" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B26" s="58"/>
-      <c r="C26" s="58"/>
+      <c r="B26" s="51"/>
+      <c r="C26" s="51"/>
     </row>
     <row r="65" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="D4:I4"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D4:I4"/>
   </mergeCells>
   <pageMargins left="0.5" right="1" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
